--- a/maintenance_forms/022_site_maintenance_team_task_risk_assessment--maintenance_forms.xlsx
+++ b/maintenance_forms/022_site_maintenance_team_task_risk_assessment--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'team_1',_'label':_'team_1'}</t>
+          <t>team_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'team_1', 'label': 'Team 1'}</t>
+          <t>Team 1</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'team_2',_'label':_'team_2'}</t>
+          <t>team_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'team_2', 'label': 'Team 2'}</t>
+          <t>Team 2</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'team_3',_'label':_'team_3'}</t>
+          <t>team_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'team_3', 'label': 'Team 3'}</t>
+          <t>Team 3</t>
         </is>
       </c>
     </row>
